--- a/salesforce_forms/002_customer_service_satisfaction_survey--salesforce_forms.xlsx
+++ b/salesforce_forms/002_customer_service_satisfaction_survey--salesforce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,8 +669,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,12 +698,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'not_satisfied'}</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'not_satisfied'}</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'phone_call'}</t>
+          <t>phone call</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'in_person'}</t>
+          <t>in person</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'in_store'}</t>
+          <t>in_store</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'in_store'}</t>
+          <t>in store</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_helpful'}</t>
+          <t>somewhat helpful</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'not_helpful'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'not_helpful'}</t>
+          <t>not helpful</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'very_helpful'}</t>
+          <t>very helpful</t>
         </is>
       </c>
     </row>
